--- a/SensitivityAnalysis/SingleSNP/MR_res_continuous.xlsx
+++ b/SensitivityAnalysis/SingleSNP/MR_res_continuous.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="25">
   <si>
     <t>id.exposure</t>
   </si>
@@ -42,13 +42,19 @@
     <t>nsnp</t>
   </si>
   <si>
-    <t>b</t>
+    <t>Estimate</t>
   </si>
   <si>
     <t>se</t>
   </si>
   <si>
     <t>pval</t>
+  </si>
+  <si>
+    <t>CI_LOW</t>
+  </si>
+  <si>
+    <t>CI_HIGH</t>
   </si>
   <si>
     <t>1</t>
@@ -167,37 +173,49 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1624007727418648</v>
+        <v>1.1223200587465914</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1352777072070465</v>
+        <v>0.16888098161749968</v>
       </c>
       <c r="J2" t="n">
-        <v>8.494902662900146E-18</v>
+        <v>3.0192841451298885E-11</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.791313334776292</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.4533267827168908</v>
       </c>
     </row>
   </sheetData>
@@ -239,37 +257,49 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008512829278187443</v>
+        <v>0.0877421483725683</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1083716859431957</v>
+        <v>0.1334287103353961</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9373888460806956</v>
+        <v>0.5107979477645415</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.17377812388480804</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3492624206299446</v>
       </c>
     </row>
   </sheetData>
@@ -311,37 +341,49 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.11102011325762284</v>
+        <v>0.27325757477404394</v>
       </c>
       <c r="I2" t="n">
-        <v>0.11346480408830312</v>
+        <v>0.13939426595439044</v>
       </c>
       <c r="J2" t="n">
-        <v>0.32784973654400446</v>
+        <v>0.0499582260759635</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.481350343865653E-5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5464703360446492</v>
       </c>
     </row>
   </sheetData>
@@ -383,37 +425,49 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07577493159722157</v>
+        <v>0.13333725664524057</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1063864245988427</v>
+        <v>0.1312831774634506</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4763029924931425</v>
+        <v>0.3097979093668455</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.12397777118312261</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3906522844736038</v>
       </c>
     </row>
   </sheetData>
@@ -455,37 +509,49 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
         <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0982968670848355</v>
+        <v>0.15638141832054703</v>
       </c>
       <c r="I2" t="n">
-        <v>0.10776909444196162</v>
+        <v>0.13302688337147908</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3617127764118768</v>
+        <v>0.23976973988461217</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.10435127308755199</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.41711410972864604</v>
       </c>
     </row>
   </sheetData>
@@ -527,37 +593,49 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.24918519705330666</v>
+        <v>-0.17690546590085632</v>
       </c>
       <c r="I2" t="n">
-        <v>0.10304191945707335</v>
+        <v>0.1273638928227786</v>
       </c>
       <c r="J2" t="n">
-        <v>0.015593662811329106</v>
+        <v>0.16483986790986663</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.42653869583350235</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.07272776403178974</v>
       </c>
     </row>
   </sheetData>
@@ -599,37 +677,49 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.35810527447639445</v>
+        <v>0.3709554289082515</v>
       </c>
       <c r="I2" t="n">
-        <v>0.10607843707111986</v>
+        <v>0.13088325004912582</v>
       </c>
       <c r="J2" t="n">
-        <v>7.358706251572403E-4</v>
+        <v>0.004593384631532299</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.11442425881196489</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6274865990045382</v>
       </c>
     </row>
   </sheetData>
@@ -671,37 +761,49 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.16829708387637798</v>
+        <v>-0.06834058643413997</v>
       </c>
       <c r="I2" t="n">
-        <v>0.10482869503472288</v>
+        <v>0.1296408205103432</v>
       </c>
       <c r="J2" t="n">
-        <v>0.10839511163718046</v>
+        <v>0.5980871353310928</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.32243659463441265</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1857554217661327</v>
       </c>
     </row>
   </sheetData>
@@ -743,37 +845,49 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.17760664607391982</v>
+        <v>0.2166964060296282</v>
       </c>
       <c r="I2" t="n">
-        <v>0.10833582535485235</v>
+        <v>0.13382151124200972</v>
       </c>
       <c r="J2" t="n">
-        <v>0.10112826420284307</v>
+        <v>0.10538396349417543</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.04559375600471083</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.4789865680639672</v>
       </c>
     </row>
   </sheetData>
@@ -815,37 +929,49 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.04263309981301886</v>
+        <v>-0.014720204437811198</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1082452371996485</v>
+        <v>0.13362474113484446</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6936869226960163</v>
+        <v>0.9122818734928491</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.27662469706210635</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.24718428818648397</v>
       </c>
     </row>
   </sheetData>
@@ -887,37 +1013,49 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>-8.667844400134933E-4</v>
+        <v>-0.09635675507355819</v>
       </c>
       <c r="I2" t="n">
-        <v>0.12129272744307758</v>
+        <v>0.149885261328127</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9942981904157269</v>
+        <v>0.5203083829661126</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.3901318672766871</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.19741835712957073</v>
       </c>
     </row>
   </sheetData>
